--- a/data_voor_swing/gebiedsdefinities/kern.xlsx
+++ b/data_voor_swing/gebiedsdefinities/kern.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D296"/>
+  <dimension ref="A1:D291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,12 +561,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Beringen-mijn</t>
+          <t>Beringen-mijn-tuinwijk-Koersel</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Beringen-mijn</t>
+          <t>Beringen-mijn-tuinwijk-Koersel</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oud-Waterschei</t>
+          <t>Oud Winterslag</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Oud-Waterschei</t>
+          <t>Oud Winterslag</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oud-Winterslag</t>
+          <t>Oud Waterschei</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Oud-Winterslag</t>
+          <t>Oud Waterschei</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Herk-De-Stad</t>
+          <t>Herk-de-Stad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Herk-De-Stad</t>
+          <t>Herk-de-Stad</t>
         </is>
       </c>
     </row>
@@ -1696,17 +1696,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>71034_4</t>
+          <t>71037_1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Strooiendorp</t>
+          <t>Genenbos</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Strooiendorp</t>
+          <t>Genenbos</t>
         </is>
       </c>
     </row>
@@ -1716,17 +1716,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>71037_1</t>
+          <t>71037_2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Genenbos</t>
+          <t>Linkhout</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Genenbos</t>
+          <t>Linkhout</t>
         </is>
       </c>
     </row>
@@ -1736,17 +1736,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>71037_2</t>
+          <t>71037_3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Linkhout</t>
+          <t>Lummen</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Linkhout</t>
+          <t>Lummen</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>71037_3</t>
+          <t>71037_4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lummen</t>
+          <t>Meldert</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Lummen</t>
+          <t>Meldert</t>
         </is>
       </c>
     </row>
@@ -1776,17 +1776,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>71037_4</t>
+          <t>71037_5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Meldert</t>
+          <t>Schalbroek</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Meldert</t>
+          <t>Schalbroek</t>
         </is>
       </c>
     </row>
@@ -1796,17 +1796,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>71037_5</t>
+          <t>71037_6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Schalbroek</t>
+          <t>Tiewinkel</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Schalbroek</t>
+          <t>Tiewinkel</t>
         </is>
       </c>
     </row>
@@ -1816,17 +1816,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>71037_6</t>
+          <t>71045_1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tiewinkel</t>
+          <t>Binderveld</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tiewinkel</t>
+          <t>Binderveld</t>
         </is>
       </c>
     </row>
@@ -1836,17 +1836,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>71045_1</t>
+          <t>71045_2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Binderveld</t>
+          <t>Kozen</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Binderveld</t>
+          <t>Kozen</t>
         </is>
       </c>
     </row>
@@ -1856,17 +1856,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>71045_2</t>
+          <t>71045_3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kozen</t>
+          <t>Nieuwerkerken</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Kozen</t>
+          <t>Nieuwerkerken</t>
         </is>
       </c>
     </row>
@@ -1876,17 +1876,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>71045_3</t>
+          <t>71045_4</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nieuwerkerken</t>
+          <t>Wijer</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Nieuwerkerken</t>
+          <t>Wijer</t>
         </is>
       </c>
     </row>
@@ -1896,17 +1896,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>71045_4</t>
+          <t>71053_1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wijer</t>
+          <t>Aalst</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wijer</t>
+          <t>Aalst</t>
         </is>
       </c>
     </row>
@@ -1916,17 +1916,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>71053_1</t>
+          <t>71053_10</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Aalst</t>
+          <t>Kerkom-bij-Sint-Truiden</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Aalst</t>
+          <t>Kerkom-bij-Sint-Truiden</t>
         </is>
       </c>
     </row>
@@ -1936,17 +1936,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>71053_10</t>
+          <t>71053_12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kerkom-bij-Sint-Truiden</t>
+          <t>Ordingen</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kerkom-bij-Sint-Truiden</t>
+          <t>Ordingen</t>
         </is>
       </c>
     </row>
@@ -1956,17 +1956,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>71053_11</t>
+          <t>71053_13</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Melveren</t>
+          <t>Runkelen</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Melveren</t>
+          <t>Runkelen</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>71053_12</t>
+          <t>71053_14</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ordingen</t>
+          <t>Senselberg</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ordingen</t>
+          <t>Senselberg</t>
         </is>
       </c>
     </row>
@@ -1996,17 +1996,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>71053_13</t>
+          <t>71053_15</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Runkelen</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Runkelen</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
     </row>
@@ -2016,17 +2016,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>71053_14</t>
+          <t>71053_16</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Senselberg</t>
+          <t>Velm</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Senselberg</t>
+          <t>Velm</t>
         </is>
       </c>
     </row>
@@ -2036,17 +2036,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>71053_15</t>
+          <t>71053_17</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Wilderen</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Wilderen</t>
         </is>
       </c>
     </row>
@@ -2056,17 +2056,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>71053_16</t>
+          <t>71053_18</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Velm</t>
+          <t>Zepperen</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Velm</t>
+          <t>Zepperen</t>
         </is>
       </c>
     </row>
@@ -2076,17 +2076,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>71053_17</t>
+          <t>71053_2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wilderen</t>
+          <t>Bevingen</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Wilderen</t>
+          <t>Bevingen</t>
         </is>
       </c>
     </row>
@@ -2096,17 +2096,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>71053_18</t>
+          <t>71053_3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Zepperen</t>
+          <t>Brustem</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Zepperen</t>
+          <t>Brustem</t>
         </is>
       </c>
     </row>
@@ -2116,17 +2116,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>71053_2</t>
+          <t>71053_4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bevingen</t>
+          <t>Duras</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Bevingen</t>
+          <t>Duras</t>
         </is>
       </c>
     </row>
@@ -2136,17 +2136,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>71053_3</t>
+          <t>71053_5</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brustem</t>
+          <t>Engelmanshoven</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Brustem</t>
+          <t>Engelmanshoven</t>
         </is>
       </c>
     </row>
@@ -2156,17 +2156,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>71053_4</t>
+          <t>71053_6</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Duras</t>
+          <t>Gelinden</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Duras</t>
+          <t>Gelinden</t>
         </is>
       </c>
     </row>
@@ -2176,17 +2176,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>71053_5</t>
+          <t>71053_7</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Engelmanshoven</t>
+          <t>Gorsem</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Engelmanshoven</t>
+          <t>Gorsem</t>
         </is>
       </c>
     </row>
@@ -2196,17 +2196,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>71053_6</t>
+          <t>71053_8</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Gelinden</t>
+          <t>Groot-Gelmen</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Gelinden</t>
+          <t>Groot-Gelmen</t>
         </is>
       </c>
     </row>
@@ -2216,17 +2216,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>71053_7</t>
+          <t>71053_9</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gorsem</t>
+          <t>Halmaal</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Gorsem</t>
+          <t>Halmaal</t>
         </is>
       </c>
     </row>
@@ -2236,17 +2236,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>71053_8</t>
+          <t>71057_1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Groot-Gelmen</t>
+          <t>Engsbergen</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Groot-Gelmen</t>
+          <t>Engsbergen</t>
         </is>
       </c>
     </row>
@@ -2256,17 +2256,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>71053_9</t>
+          <t>71057_2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Halmaal</t>
+          <t>Hulst</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Halmaal</t>
+          <t>Hulst</t>
         </is>
       </c>
     </row>
@@ -2276,17 +2276,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>71057_1</t>
+          <t>71057_3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Engsbergen</t>
+          <t>Schoot</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Engsbergen</t>
+          <t>Schoot</t>
         </is>
       </c>
     </row>
@@ -2296,17 +2296,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>71057_2</t>
+          <t>71057_4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hulst</t>
+          <t>Tessenderlo</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Hulst</t>
+          <t>Tessenderlo</t>
         </is>
       </c>
     </row>
@@ -2316,17 +2316,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>71057_3</t>
+          <t>71066_1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Schoot</t>
+          <t>Halveweg</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Schoot</t>
+          <t>Halveweg</t>
         </is>
       </c>
     </row>
@@ -2336,17 +2336,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>71057_4</t>
+          <t>71066_2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tessenderlo</t>
+          <t>Ter Donk</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tessenderlo</t>
+          <t>Ter Donk</t>
         </is>
       </c>
     </row>
@@ -2356,17 +2356,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>71066_1</t>
+          <t>71066_3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Halveweg</t>
+          <t>Termolen</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Halveweg</t>
+          <t>Termolen</t>
         </is>
       </c>
     </row>
@@ -2376,17 +2376,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>71066_2</t>
+          <t>71066_4</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ter Donk</t>
+          <t>Zonhoven</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Ter Donk</t>
+          <t>Zonhoven</t>
         </is>
       </c>
     </row>
@@ -2396,17 +2396,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>71066_3</t>
+          <t>71067_1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Termolen</t>
+          <t>Bessemer</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Termolen</t>
+          <t>Bessemer</t>
         </is>
       </c>
     </row>
@@ -2416,17 +2416,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>71066_4</t>
+          <t>71067_2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Zonhoven</t>
+          <t>Papendaal</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Zonhoven</t>
+          <t>Papendaal</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2436,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>71067_1</t>
+          <t>71067_3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bessemer</t>
+          <t>Wiemesmeer</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Bessemer</t>
+          <t>Wiemesmeer</t>
         </is>
       </c>
     </row>
@@ -2456,17 +2456,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>71067_2</t>
+          <t>71067_4</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Papendaal</t>
+          <t>Zutendaal</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Papendaal</t>
+          <t>Zutendaal</t>
         </is>
       </c>
     </row>
@@ -2476,17 +2476,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>71067_3</t>
+          <t>71069_1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wiemesmeer</t>
+          <t>Genendijk</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Wiemesmeer</t>
+          <t>Genendijk</t>
         </is>
       </c>
     </row>
@@ -2496,17 +2496,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>71067_4</t>
+          <t>71069_2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Zutendaal</t>
+          <t>Kwaadmechelen</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Zutendaal</t>
+          <t>Kwaadmechelen</t>
         </is>
       </c>
     </row>
@@ -2516,17 +2516,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>71069_1</t>
+          <t>71069_3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Genendijk</t>
+          <t>Oostham</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Genendijk</t>
+          <t>Oostham</t>
         </is>
       </c>
     </row>
@@ -2536,17 +2536,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>71069_2</t>
+          <t>71070_1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kwaadmechelen</t>
+          <t>Heusden + Berkenbos</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Kwaadmechelen</t>
+          <t>Heusden + Berkenbos</t>
         </is>
       </c>
     </row>
@@ -2556,17 +2556,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>71069_3</t>
+          <t>71070_2</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Oostham</t>
+          <t>Boekt</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Oostham</t>
+          <t>Boekt</t>
         </is>
       </c>
     </row>
@@ -2576,17 +2576,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>71070_1</t>
+          <t>71070_3</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Berkenbos</t>
+          <t>Bolderberg</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Berkenbos</t>
+          <t>Bolderberg</t>
         </is>
       </c>
     </row>
@@ -2596,17 +2596,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>71070_2</t>
+          <t>71070_4</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boekt</t>
+          <t>Eversel</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Boekt</t>
+          <t>Eversel</t>
         </is>
       </c>
     </row>
@@ -2616,17 +2616,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>71070_3</t>
+          <t>71070_6</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bolderberg</t>
+          <t>Lindeman</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Bolderberg</t>
+          <t>Lindeman</t>
         </is>
       </c>
     </row>
@@ -2636,17 +2636,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>71070_4</t>
+          <t>71070_7</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Eversel</t>
+          <t>Viversel</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Eversel</t>
+          <t>Viversel</t>
         </is>
       </c>
     </row>
@@ -2656,17 +2656,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>71070_5</t>
+          <t>71070_8</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Heusden</t>
+          <t>Voort</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Heusden</t>
+          <t>Voort</t>
         </is>
       </c>
     </row>
@@ -2676,17 +2676,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>71070_6</t>
+          <t>71070_9</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lindeman</t>
+          <t>Zolder</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Lindeman</t>
+          <t>Zolder</t>
         </is>
       </c>
     </row>
@@ -2696,17 +2696,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>71070_7</t>
+          <t>72003_1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Viversel</t>
+          <t>Bocholt</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Viversel</t>
+          <t>Bocholt</t>
         </is>
       </c>
     </row>
@@ -2716,17 +2716,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>71070_8</t>
+          <t>72003_2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Voort</t>
+          <t>De Hees</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Voort</t>
+          <t>De Hees</t>
         </is>
       </c>
     </row>
@@ -2736,17 +2736,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>71070_9</t>
+          <t>72003_3</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Zolder</t>
+          <t>Kaulille</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Zolder</t>
+          <t>Kaulille</t>
         </is>
       </c>
     </row>
@@ -2756,17 +2756,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>72003_1</t>
+          <t>72003_4</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bocholt</t>
+          <t>Lozen</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Bocholt</t>
+          <t>Lozen</t>
         </is>
       </c>
     </row>
@@ -2776,17 +2776,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>72003_2</t>
+          <t>72003_5</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>De Hees</t>
+          <t>Neerkreiel</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>De Hees</t>
+          <t>Neerkreiel</t>
         </is>
       </c>
     </row>
@@ -2796,17 +2796,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>72003_3</t>
+          <t>72004_1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kaulille</t>
+          <t>Beek</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Kaulille</t>
+          <t>Beek</t>
         </is>
       </c>
     </row>
@@ -2816,17 +2816,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>72003_4</t>
+          <t>72004_2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lozen</t>
+          <t>Bree</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Lozen</t>
+          <t>Bree</t>
         </is>
       </c>
     </row>
@@ -2836,17 +2836,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>72003_5</t>
+          <t>72004_3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Neerkreiel</t>
+          <t>Opitter</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Neerkreiel</t>
+          <t>Opitter</t>
         </is>
       </c>
     </row>
@@ -2856,17 +2856,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>72004_1</t>
+          <t>72004_4</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Beek</t>
+          <t>Tongerlo</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Beek</t>
+          <t>Tongerlo</t>
         </is>
       </c>
     </row>
@@ -2876,17 +2876,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>72004_2</t>
+          <t>72004_5</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bree</t>
+          <t>Vostaard</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Bree</t>
+          <t>Vostaard</t>
         </is>
       </c>
     </row>
@@ -2896,17 +2896,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>72004_3</t>
+          <t>72018_1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Opitter</t>
+          <t>Geistingen</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Opitter</t>
+          <t>Geistingen</t>
         </is>
       </c>
     </row>
@@ -2916,17 +2916,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>72004_4</t>
+          <t>72018_2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tongerlo</t>
+          <t>Kessenich</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tongerlo</t>
+          <t>Kessenich</t>
         </is>
       </c>
     </row>
@@ -2936,17 +2936,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>72004_5</t>
+          <t>72018_3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Vostaard</t>
+          <t>Kinrooi</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Vostaard</t>
+          <t>Kinrooi</t>
         </is>
       </c>
     </row>
@@ -2956,17 +2956,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>72018_1</t>
+          <t>72018_4</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Geistingen</t>
+          <t>Molenbeersel</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Geistingen</t>
+          <t>Molenbeersel</t>
         </is>
       </c>
     </row>
@@ -2976,17 +2976,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>72018_2</t>
+          <t>72018_5</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Kessenich</t>
+          <t>Ophoven</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Kessenich</t>
+          <t>Ophoven</t>
         </is>
       </c>
     </row>
@@ -2996,17 +2996,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>72018_3</t>
+          <t>72020_1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Kinrooi</t>
+          <t>Grote Barrier</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Kinrooi</t>
+          <t>Grote Barrier</t>
         </is>
       </c>
     </row>
@@ -3016,17 +3016,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>72018_4</t>
+          <t>72020_10</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Molenbeersel</t>
+          <t>Stevensvennen</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Molenbeersel</t>
+          <t>Stevensvennen</t>
         </is>
       </c>
     </row>
@@ -3036,17 +3036,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>72018_5</t>
+          <t>72020_11</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ophoven</t>
+          <t>Weiwortels</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Ophoven</t>
+          <t>Weiwortels</t>
         </is>
       </c>
     </row>
@@ -3056,17 +3056,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>72020_1</t>
+          <t>72020_2</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Grote Barrier</t>
+          <t>Heide</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Grote Barrier</t>
+          <t>Heide</t>
         </is>
       </c>
     </row>
@@ -3076,17 +3076,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>72020_10</t>
+          <t>72020_3</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Stevensvennen</t>
+          <t>Heuvel</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Stevensvennen</t>
+          <t>Heuvel</t>
         </is>
       </c>
     </row>
@@ -3096,17 +3096,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>72020_2</t>
+          <t>72020_4</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Heide</t>
+          <t>Kattenbos</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Heide</t>
+          <t>Kattenbos</t>
         </is>
       </c>
     </row>
@@ -3116,17 +3116,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>72020_3</t>
+          <t>72020_5</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Heuvel</t>
+          <t>Kerkhoven</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Heuvel</t>
+          <t>Kerkhoven</t>
         </is>
       </c>
     </row>
@@ -3136,17 +3136,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>72020_4</t>
+          <t>72020_6</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kattenbos</t>
+          <t>Kolonie</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Kattenbos</t>
+          <t>Kolonie</t>
         </is>
       </c>
     </row>
@@ -3156,17 +3156,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>72020_5</t>
+          <t>72020_7</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Kerkhoven</t>
+          <t>Lommel</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Kerkhoven</t>
+          <t>Lommel</t>
         </is>
       </c>
     </row>
@@ -3176,17 +3176,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>72020_6</t>
+          <t>72020_8</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Kolonie</t>
+          <t>Lommel-Werkplaatsen</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Kolonie</t>
+          <t>Lommel-Werkplaatsen</t>
         </is>
       </c>
     </row>
@@ -3196,17 +3196,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>72020_7</t>
+          <t>72020_9</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Lommel</t>
+          <t>Lutlommel-centrum</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Lommel</t>
+          <t>Lutlommel-centrum</t>
         </is>
       </c>
     </row>
@@ -3216,17 +3216,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>72020_8</t>
+          <t>72021_1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Lommel-Werkplaatsen</t>
+          <t>Aldeneik</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Lommel-Werkplaatsen</t>
+          <t>Aldeneik</t>
         </is>
       </c>
     </row>
@@ -3236,17 +3236,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>72020_9</t>
+          <t>72021_2</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Lutlommel</t>
+          <t>Dorne</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Lutlommel</t>
+          <t>Dorne</t>
         </is>
       </c>
     </row>
@@ -3256,17 +3256,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>72021_1</t>
+          <t>72021_3</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Aldeneik</t>
+          <t>Maaseik</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Aldeneik</t>
+          <t>Maaseik</t>
         </is>
       </c>
     </row>
@@ -3276,17 +3276,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>72021_2</t>
+          <t>72021_4</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Dorne</t>
+          <t>Neeroeteren</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Dorne</t>
+          <t>Neeroeteren</t>
         </is>
       </c>
     </row>
@@ -3296,17 +3296,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>72021_3</t>
+          <t>72021_5</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Maaseik</t>
+          <t>Opoeteren</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Maaseik</t>
+          <t>Opoeteren</t>
         </is>
       </c>
     </row>
@@ -3316,17 +3316,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>72021_4</t>
+          <t>72021_6</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Neeroeteren</t>
+          <t>Voorshoven + Neerhoven</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Neeroeteren</t>
+          <t>Voorshoven + Neerhoven</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>72021_5</t>
+          <t>72021_7</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Opoeteren</t>
+          <t>Wurfeld</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Opoeteren</t>
+          <t>Wurfeld</t>
         </is>
       </c>
     </row>
@@ -3356,17 +3356,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>72021_6</t>
+          <t>72030_1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Voorshoven Neerhoven</t>
+          <t>Grote Brogel</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Voorshoven Neerhoven</t>
+          <t>Grote Brogel</t>
         </is>
       </c>
     </row>
@@ -3376,17 +3376,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>72021_7</t>
+          <t>72030_2</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Wurfeld</t>
+          <t>Kleine Brogel</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Wurfeld</t>
+          <t>Kleine Brogel</t>
         </is>
       </c>
     </row>
@@ -3396,17 +3396,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>72030_1</t>
+          <t>72030_3</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Grote Brogel</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Grote Brogel</t>
+          <t>Linde</t>
         </is>
       </c>
     </row>
@@ -3416,17 +3416,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>72030_2</t>
+          <t>72030_4</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Kleine Brogel</t>
+          <t>Peer</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Kleine Brogel</t>
+          <t>Peer</t>
         </is>
       </c>
     </row>
@@ -3436,17 +3436,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>72030_3</t>
+          <t>72030_5</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Wauberg</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Wauberg</t>
         </is>
       </c>
     </row>
@@ -3456,17 +3456,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>72030_4</t>
+          <t>72030_6</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Peer</t>
+          <t>Wijchmaal</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Peer</t>
+          <t>Wijchmaal</t>
         </is>
       </c>
     </row>
@@ -3476,17 +3476,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>72030_5</t>
+          <t>72037_1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wauberg</t>
+          <t>Achel</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Wauberg</t>
+          <t>Achel</t>
         </is>
       </c>
     </row>
@@ -3496,17 +3496,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>72030_6</t>
+          <t>72037_2</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Wijchmaal</t>
+          <t>Hamont</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Wijchmaal</t>
+          <t>Hamont</t>
         </is>
       </c>
     </row>
@@ -3516,17 +3516,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>72037_1</t>
+          <t>72037_3</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Achel</t>
+          <t>Rodenrijt</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Achel</t>
+          <t>Rodenrijt</t>
         </is>
       </c>
     </row>
@@ -3536,17 +3536,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>72037_2</t>
+          <t>72037_4</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Hamont</t>
+          <t>'t Lo</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Hamont</t>
+          <t>'t Lo</t>
         </is>
       </c>
     </row>
@@ -3556,17 +3556,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>72037_3</t>
+          <t>72038_1</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Rodenrijt</t>
+          <t>Eksel</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Rodenrijt</t>
+          <t>Eksel</t>
         </is>
       </c>
     </row>
@@ -3576,17 +3576,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>72037_4</t>
+          <t>72038_2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>'t Lo</t>
+          <t>Hechtel</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>'t Lo</t>
+          <t>Hechtel</t>
         </is>
       </c>
     </row>
@@ -3596,17 +3596,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>72038_1</t>
+          <t>72038_3</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Eksel</t>
+          <t>Hoef</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Eksel</t>
+          <t>Hoef</t>
         </is>
       </c>
     </row>
@@ -3616,17 +3616,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>72038_2</t>
+          <t>72039_1</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Hechtel</t>
+          <t>Helchteren</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Hechtel</t>
+          <t>Helchteren</t>
         </is>
       </c>
     </row>
@@ -3636,17 +3636,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>72038_3</t>
+          <t>72039_2</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Hoef</t>
+          <t>Houthalen</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Hoef</t>
+          <t>Houthalen</t>
         </is>
       </c>
     </row>
@@ -3656,17 +3656,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>72039_1</t>
+          <t>72039_3</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Helchteren</t>
+          <t>Houthalen-Oost</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Helchteren</t>
+          <t>Houthalen-Oost</t>
         </is>
       </c>
     </row>
@@ -3676,17 +3676,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>72039_2</t>
+          <t>72039_5</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Houthalen</t>
+          <t>Lillo</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Houthalen</t>
+          <t>Lillo</t>
         </is>
       </c>
     </row>
@@ -3696,17 +3696,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>72039_3</t>
+          <t>72039_6</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Houthalen-Oost</t>
+          <t>Meulenberg</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Houthalen-Oost</t>
+          <t>Meulenberg</t>
         </is>
       </c>
     </row>
@@ -3716,17 +3716,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>72039_5</t>
+          <t>72039_7</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Lillo</t>
+          <t>Sonnis</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Lillo</t>
+          <t>Sonnis</t>
         </is>
       </c>
     </row>
@@ -3736,17 +3736,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>72039_6</t>
+          <t>72041_1</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Meulenberg</t>
+          <t>Dilsen</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Meulenberg</t>
+          <t>Dilsen</t>
         </is>
       </c>
     </row>
@@ -3756,17 +3756,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>72039_7</t>
+          <t>72041_2</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Sonnis</t>
+          <t>Elen</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Sonnis</t>
+          <t>Elen</t>
         </is>
       </c>
     </row>
@@ -3776,17 +3776,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>72041_1</t>
+          <t>72041_3</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Dilsen</t>
+          <t>Lanklaar</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Dilsen</t>
+          <t>Lanklaar</t>
         </is>
       </c>
     </row>
@@ -3796,17 +3796,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>72041_2</t>
+          <t>72041_5</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Elen</t>
+          <t>Rotem</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Elen</t>
+          <t>Rotem</t>
         </is>
       </c>
     </row>
@@ -3816,17 +3816,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>72041_3</t>
+          <t>72041_6</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Lanklaar</t>
+          <t>Stokkem</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Lanklaar</t>
+          <t>Stokkem</t>
         </is>
       </c>
     </row>
@@ -3836,17 +3836,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>72041_5</t>
+          <t>72042_1</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Rotem</t>
+          <t>Ellikom</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Rotem</t>
+          <t>Ellikom</t>
         </is>
       </c>
     </row>
@@ -3856,17 +3856,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>72041_6</t>
+          <t>72042_2</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Stokkem</t>
+          <t>Gruitrode</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Stokkem</t>
+          <t>Gruitrode</t>
         </is>
       </c>
     </row>
@@ -3876,17 +3876,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>72042_1</t>
+          <t>72042_3</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ellikom</t>
+          <t>Louwel</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Ellikom</t>
+          <t>Louwel</t>
         </is>
       </c>
     </row>
@@ -3896,17 +3896,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>72042_2</t>
+          <t>72042_4</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Gruitrode</t>
+          <t>Meeuwen</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Gruitrode</t>
+          <t>Meeuwen</t>
         </is>
       </c>
     </row>
@@ -3916,17 +3916,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>72042_3</t>
+          <t>72042_5</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Louwel</t>
+          <t>Neerglabbeek</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Louwel</t>
+          <t>Neerglabbeek</t>
         </is>
       </c>
     </row>
@@ -3936,17 +3936,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>72042_4</t>
+          <t>72042_6</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Meeuwen</t>
+          <t>Nieuwe Kempen</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Meeuwen</t>
+          <t>Nieuwe Kempen</t>
         </is>
       </c>
     </row>
@@ -3956,17 +3956,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>72042_5</t>
+          <t>72042_7</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Neerglabbeek</t>
+          <t>Opglabbeek</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Neerglabbeek</t>
+          <t>Opglabbeek</t>
         </is>
       </c>
     </row>
@@ -3976,17 +3976,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>72042_6</t>
+          <t>72042_8</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Nieuwe Kempen</t>
+          <t>Wijshagen</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Nieuwe Kempen</t>
+          <t>Wijshagen</t>
         </is>
       </c>
     </row>
@@ -3996,17 +3996,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>72042_7</t>
+          <t>72043_1</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Opglabbeek</t>
+          <t>Damsheide</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Opglabbeek</t>
+          <t>Damsheide</t>
         </is>
       </c>
     </row>
@@ -4016,17 +4016,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>72042_8</t>
+          <t>72043_2</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wijshagen</t>
+          <t>Grote Heide</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Wijshagen</t>
+          <t>Grote Heide</t>
         </is>
       </c>
     </row>
@@ -4036,17 +4036,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>72043_1</t>
+          <t>72043_3</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Damsheide</t>
+          <t>Herent</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Damsheide</t>
+          <t>Herent</t>
         </is>
       </c>
     </row>
@@ -4056,17 +4056,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>72043_2</t>
+          <t>72043_4</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Grote Heide</t>
+          <t>Holheide</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Grote Heide</t>
+          <t>Holheide</t>
         </is>
       </c>
     </row>
@@ -4076,17 +4076,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>72043_3</t>
+          <t>72043_5</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Herent</t>
+          <t>Lindel</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Herent</t>
+          <t>Lindel</t>
         </is>
       </c>
     </row>
@@ -4096,17 +4096,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>72043_4</t>
+          <t>72043_6</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Holheide</t>
+          <t>Neerpelt-Overpelt</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Holheide</t>
+          <t>Neerpelt-Overpelt</t>
         </is>
       </c>
     </row>
@@ -4116,17 +4116,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>72043_5</t>
+          <t>72043_7</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Lindel</t>
+          <t>Overpelt-Fabriek</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Lindel</t>
+          <t>Overpelt-Fabriek</t>
         </is>
       </c>
     </row>
@@ -4136,17 +4136,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>72043_6</t>
+          <t>72043_9</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Neerpelt</t>
+          <t>Sint-Huibrechts-Lille</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Neerpelt</t>
+          <t>Sint-Huibrechts-Lille</t>
         </is>
       </c>
     </row>
@@ -4156,17 +4156,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>72043_7</t>
+          <t>73001_1</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Overpelt</t>
+          <t>Alken + Alken-Station</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Overpelt</t>
+          <t>Alken + Alken-Station</t>
         </is>
       </c>
     </row>
@@ -4176,17 +4176,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>72043_8</t>
+          <t>73001_3</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Overpelt Fabriek</t>
+          <t>Sint-Joris</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Overpelt Fabriek</t>
+          <t>Sint-Joris</t>
         </is>
       </c>
     </row>
@@ -4196,17 +4196,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>72043_9</t>
+          <t>73001_4</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Sint-Huibrechts-Lille</t>
+          <t>Terkoest</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Sint-Huibrechts-Lille</t>
+          <t>Terkoest</t>
         </is>
       </c>
     </row>
@@ -4216,17 +4216,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>73001_1</t>
+          <t>73006_1</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Alken</t>
+          <t>Beverst</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Alken</t>
+          <t>Beverst</t>
         </is>
       </c>
     </row>
@@ -4236,17 +4236,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>73001_2</t>
+          <t>73006_10</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Alken-Station</t>
+          <t>Rijkhoven</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Alken-Station</t>
+          <t>Rijkhoven</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>73001_3</t>
+          <t>73006_11</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Sint-Joris</t>
+          <t>Rosmeer</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Sint-Joris</t>
+          <t>Rosmeer</t>
         </is>
       </c>
     </row>
@@ -4276,17 +4276,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>73001_4</t>
+          <t>73006_12</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Terkoest</t>
+          <t>Schoonbeek</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Terkoest</t>
+          <t>Schoonbeek</t>
         </is>
       </c>
     </row>
@@ -4296,17 +4296,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>73006_1</t>
+          <t>73006_13</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Beverst</t>
+          <t>Waltwilder</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Beverst</t>
+          <t>Waltwilder</t>
         </is>
       </c>
     </row>
@@ -4316,17 +4316,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>73006_10</t>
+          <t>73006_2</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Rijkhoven</t>
+          <t>Bilzen</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Rijkhoven</t>
+          <t>Bilzen</t>
         </is>
       </c>
     </row>
@@ -4336,17 +4336,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>73006_11</t>
+          <t>73006_3</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Rosmeer</t>
+          <t>Eigenbilzen - Mopertingen</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Rosmeer</t>
+          <t>Eigenbilzen - Mopertingen</t>
         </is>
       </c>
     </row>
@@ -4356,17 +4356,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>73006_12</t>
+          <t>73006_4</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Schoonbeek</t>
+          <t>Grote Spouwen</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Schoonbeek</t>
+          <t>Grote Spouwen</t>
         </is>
       </c>
     </row>
@@ -4376,17 +4376,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>73006_13</t>
+          <t>73006_5</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Waltwilder</t>
+          <t>Hees</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Waltwilder</t>
+          <t>Hees</t>
         </is>
       </c>
     </row>
@@ -4396,17 +4396,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>73006_2</t>
+          <t>73006_6</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bilzen</t>
+          <t>Hoelbeek</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Bilzen</t>
+          <t>Hoelbeek</t>
         </is>
       </c>
     </row>
@@ -4416,17 +4416,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>73006_3</t>
+          <t>73006_7</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Eigenbilzen-Mopertingen</t>
+          <t>Kleine Spouwen</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Eigenbilzen-Mopertingen</t>
+          <t>Kleine Spouwen</t>
         </is>
       </c>
     </row>
@@ -4436,17 +4436,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>73006_4</t>
+          <t>73006_8</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Grote Spouwen</t>
+          <t>Martenslinde</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Grote Spouwen</t>
+          <t>Martenslinde</t>
         </is>
       </c>
     </row>
@@ -4456,17 +4456,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>73006_5</t>
+          <t>73006_9</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Hees</t>
+          <t>Munsterbilzen</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Hees</t>
+          <t>Munsterbilzen</t>
         </is>
       </c>
     </row>
@@ -4476,17 +4476,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>73006_6</t>
+          <t>73009_1</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Hoelbeek</t>
+          <t>Bommershoven</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Hoelbeek</t>
+          <t>Bommershoven</t>
         </is>
       </c>
     </row>
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>73006_7</t>
+          <t>73009_2</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Kleine Spouwen</t>
+          <t>Borgloon</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Kleine Spouwen</t>
+          <t>Borgloon</t>
         </is>
       </c>
     </row>
@@ -4516,17 +4516,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>73006_8</t>
+          <t>73009_3</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Martenslinde</t>
+          <t>Broekom</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Martenslinde</t>
+          <t>Broekom</t>
         </is>
       </c>
     </row>
@@ -4536,17 +4536,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>73006_9</t>
+          <t>73009_4</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Munsterbilzen</t>
+          <t>Gors</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Munsterbilzen</t>
+          <t>Gors</t>
         </is>
       </c>
     </row>
@@ -4556,17 +4556,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>73009_1</t>
+          <t>73009_5</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bommershoven</t>
+          <t>Hoepertingen</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Bommershoven</t>
+          <t>Hoepertingen</t>
         </is>
       </c>
     </row>
@@ -4576,17 +4576,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>73009_2</t>
+          <t>73009_6</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Borgloon</t>
+          <t>Jesseren</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Borgloon</t>
+          <t>Jesseren</t>
         </is>
       </c>
     </row>
@@ -4596,17 +4596,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>73009_3</t>
+          <t>73009_7</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Broekom</t>
+          <t>Kerniel</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Broekom</t>
+          <t>Kerniel</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>73009_4</t>
+          <t>73009_8</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Gors</t>
+          <t>Rijkel</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Gors</t>
+          <t>Rijkel</t>
         </is>
       </c>
     </row>
@@ -4636,17 +4636,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>73009_5</t>
+          <t>73022_1</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Hoepertingen</t>
+          <t>Heers</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Hoepertingen</t>
+          <t>Heers</t>
         </is>
       </c>
     </row>
@@ -4656,17 +4656,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>73009_6</t>
+          <t>73022_2</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Jesseren</t>
+          <t>Heks</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Jesseren</t>
+          <t>Heks</t>
         </is>
       </c>
     </row>
@@ -4676,17 +4676,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>73009_7</t>
+          <t>73022_3</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Kerniel</t>
+          <t>Horpmaal</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Kerniel</t>
+          <t>Horpmaal</t>
         </is>
       </c>
     </row>
@@ -4696,17 +4696,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>73009_8</t>
+          <t>73022_4</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Rijkel</t>
+          <t>Mechelen-Bovelingen</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Rijkel</t>
+          <t>Mechelen-Bovelingen</t>
         </is>
       </c>
     </row>
@@ -4716,17 +4716,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>73022_1</t>
+          <t>73022_5</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Heers</t>
+          <t>Rukkelingen-Loon</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Heers</t>
+          <t>Rukkelingen-Loon</t>
         </is>
       </c>
     </row>
@@ -4736,17 +4736,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>73022_2</t>
+          <t>73022_6</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Heks</t>
+          <t>Vechmaal</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Heks</t>
+          <t>Vechmaal</t>
         </is>
       </c>
     </row>
@@ -4756,17 +4756,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>73022_3</t>
+          <t>73022_7</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Horpmaal</t>
+          <t>Veulen</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Horpmaal</t>
+          <t>Veulen</t>
         </is>
       </c>
     </row>
@@ -4776,17 +4776,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>73022_4</t>
+          <t>73028_1</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Mechelen-Bovelingen</t>
+          <t>Herstappe</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Mechelen-Bovelingen</t>
+          <t>Herstappe</t>
         </is>
       </c>
     </row>
@@ -4796,17 +4796,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>73022_5</t>
+          <t>73032_1</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Rukkelingen-Loon</t>
+          <t>Alt-Hoeselt</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Rukkelingen-Loon</t>
+          <t>Alt-Hoeselt</t>
         </is>
       </c>
     </row>
@@ -4816,17 +4816,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>73022_6</t>
+          <t>73032_2</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Vechmaal</t>
+          <t>Groenstraat</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Vechmaal</t>
+          <t>Groenstraat</t>
         </is>
       </c>
     </row>
@@ -4836,17 +4836,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>73022_7</t>
+          <t>73032_3</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Veulen</t>
+          <t>Hoeselt</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Veulen</t>
+          <t>Hoeselt</t>
         </is>
       </c>
     </row>
@@ -4856,17 +4856,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>73028_1</t>
+          <t>73032_4</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Herstappe</t>
+          <t>Romershoven</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Herstappe</t>
+          <t>Romershoven</t>
         </is>
       </c>
     </row>
@@ -4876,17 +4876,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>73032_1</t>
+          <t>73032_5</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Alt-Hoeselt</t>
+          <t>Schalkhoven</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Alt-Hoeselt</t>
+          <t>Schalkhoven</t>
         </is>
       </c>
     </row>
@@ -4896,17 +4896,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>73032_2</t>
+          <t>73032_6</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Groenstraat</t>
+          <t>Sint-Huibrechts-Hern</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Groenstraat</t>
+          <t>Sint-Huibrechts-Hern</t>
         </is>
       </c>
     </row>
@@ -4916,17 +4916,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>73032_3</t>
+          <t>73032_7</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Hoeselt</t>
+          <t>Werm</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Hoeselt</t>
+          <t>Werm</t>
         </is>
       </c>
     </row>
@@ -4936,17 +4936,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>73032_4</t>
+          <t>73040_1</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Romershoven</t>
+          <t>Guigoven</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Romershoven</t>
+          <t>Guigoven</t>
         </is>
       </c>
     </row>
@@ -4956,17 +4956,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>73032_5</t>
+          <t>73040_2</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Schalkhoven</t>
+          <t>Kortessem</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Schalkhoven</t>
+          <t>Kortessem</t>
         </is>
       </c>
     </row>
@@ -4976,17 +4976,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>73032_6</t>
+          <t>73040_3</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Sint-Huibrechts-Hern</t>
+          <t>Vliermaal</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Sint-Huibrechts-Hern</t>
+          <t>Vliermaal</t>
         </is>
       </c>
     </row>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>73032_7</t>
+          <t>73040_4</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Werm</t>
+          <t>Vliermaalroot</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Werm</t>
+          <t>Vliermaalroot</t>
         </is>
       </c>
     </row>
@@ -5016,17 +5016,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>73040_1</t>
+          <t>73040_5</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Guigoven</t>
+          <t>Wintershoven</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Guigoven</t>
+          <t>Wintershoven</t>
         </is>
       </c>
     </row>
@@ -5036,17 +5036,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>73040_2</t>
+          <t>73042_1</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Kortessem</t>
+          <t>Gellik</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Kortessem</t>
+          <t>Gellik</t>
         </is>
       </c>
     </row>
@@ -5056,17 +5056,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>73040_3</t>
+          <t>73042_2</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Vliermaal</t>
+          <t>Kesselt</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Vliermaal</t>
+          <t>Kesselt</t>
         </is>
       </c>
     </row>
@@ -5076,17 +5076,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>73040_4</t>
+          <t>73042_3</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Vliermaalroot</t>
+          <t>Lanaken</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Vliermaalroot</t>
+          <t>Lanaken</t>
         </is>
       </c>
     </row>
@@ -5096,17 +5096,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>73040_5</t>
+          <t>73042_4</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Wintershoven</t>
+          <t>Neerharen</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Wintershoven</t>
+          <t>Neerharen</t>
         </is>
       </c>
     </row>
@@ -5116,17 +5116,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>73042_1</t>
+          <t>73042_5</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Gellik</t>
+          <t>Rekem</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Gellik</t>
+          <t>Rekem</t>
         </is>
       </c>
     </row>
@@ -5136,17 +5136,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>73042_2</t>
+          <t>73042_6</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Kesselt</t>
+          <t>Smeermaas</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Kesselt</t>
+          <t>Smeermaas</t>
         </is>
       </c>
     </row>
@@ -5156,17 +5156,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>73042_3</t>
+          <t>73042_7</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Lanaken</t>
+          <t>Veldwezelt</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Lanaken</t>
+          <t>Veldwezelt</t>
         </is>
       </c>
     </row>
@@ -5176,17 +5176,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>73042_4</t>
+          <t>73066_1</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Neerharen</t>
+          <t>Genoelselderen</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Neerharen</t>
+          <t>Genoelselderen</t>
         </is>
       </c>
     </row>
@@ -5196,17 +5196,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>73042_5</t>
+          <t>73066_10</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Rekem</t>
+          <t>Vlijtingen</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Rekem</t>
+          <t>Vlijtingen</t>
         </is>
       </c>
     </row>
@@ -5216,17 +5216,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>73042_6</t>
+          <t>73066_11</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Smeermaas</t>
+          <t>Vroenhoven</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Smeermaas</t>
+          <t>Vroenhoven</t>
         </is>
       </c>
     </row>
@@ -5236,17 +5236,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>73042_7</t>
+          <t>73066_12</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Veldwezelt</t>
+          <t>Zichen - Zussen - Bolder</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Veldwezelt</t>
+          <t>Zichen - Zussen - Bolder</t>
         </is>
       </c>
     </row>
@@ -5256,17 +5256,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>73066_1</t>
+          <t>73066_2</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Genoelselderen</t>
+          <t>Herderen</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Genoelselderen</t>
+          <t>Herderen</t>
         </is>
       </c>
     </row>
@@ -5276,17 +5276,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>73066_10</t>
+          <t>73066_3</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Vlijtingen</t>
+          <t>Heukelom</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Vlijtingen</t>
+          <t>Heukelom</t>
         </is>
       </c>
     </row>
@@ -5296,17 +5296,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>73066_11</t>
+          <t>73066_4</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Vroenhoven</t>
+          <t>Kanne</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Vroenhoven</t>
+          <t>Kanne</t>
         </is>
       </c>
     </row>
@@ -5316,17 +5316,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>73066_12</t>
+          <t>73066_5</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Zichen-Zussen-Bolder</t>
+          <t>Lafelt</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Zichen-Zussen-Bolder</t>
+          <t>Lafelt</t>
         </is>
       </c>
     </row>
@@ -5336,17 +5336,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>73066_2</t>
+          <t>73066_6</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Herderen</t>
+          <t>Membruggen</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Herderen</t>
+          <t>Membruggen</t>
         </is>
       </c>
     </row>
@@ -5356,17 +5356,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>73066_3</t>
+          <t>73066_7</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Heukelom</t>
+          <t>Millen</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Heukelom</t>
+          <t>Millen</t>
         </is>
       </c>
     </row>
@@ -5376,17 +5376,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>73066_4</t>
+          <t>73066_8</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Kanne</t>
+          <t>Riemst</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Kanne</t>
+          <t>Riemst</t>
         </is>
       </c>
     </row>
@@ -5396,17 +5396,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>73066_5</t>
+          <t>73066_9</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Lafelt</t>
+          <t>Val - Meer</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Lafelt</t>
+          <t>Val - Meer</t>
         </is>
       </c>
     </row>
@@ -5416,17 +5416,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>73066_6</t>
+          <t>73083_1</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Membruggen</t>
+          <t>Henis</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Membruggen</t>
+          <t>Henis</t>
         </is>
       </c>
     </row>
@@ -5436,17 +5436,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>73066_7</t>
+          <t>73083_10</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Millen</t>
+          <t>Rutten</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Millen</t>
+          <t>Rutten</t>
         </is>
       </c>
     </row>
@@ -5456,17 +5456,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>73066_8</t>
+          <t>73083_11</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Riemst</t>
+          <t>'s Herenelderen</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Riemst</t>
+          <t>'s Herenelderen</t>
         </is>
       </c>
     </row>
@@ -5476,17 +5476,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>73066_9</t>
+          <t>73083_12</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Val-Meer</t>
+          <t>Sluizen</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Val-Meer</t>
+          <t>Sluizen</t>
         </is>
       </c>
     </row>
@@ -5496,17 +5496,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>73083_1</t>
+          <t>73083_13</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Henis</t>
+          <t>Tongeren</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Henis</t>
+          <t>Tongeren</t>
         </is>
       </c>
     </row>
@@ -5516,17 +5516,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>73083_10</t>
+          <t>73083_14</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Rutten</t>
+          <t>Vreren</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Rutten</t>
+          <t>Vreren</t>
         </is>
       </c>
     </row>
@@ -5536,17 +5536,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>73083_11</t>
+          <t>73083_15</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>'s Herenelderen</t>
+          <t>Widooie</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>'s Herenelderen</t>
+          <t>Widooie</t>
         </is>
       </c>
     </row>
@@ -5556,17 +5556,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>73083_12</t>
+          <t>73083_2</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Sluizen</t>
+          <t>Ketsingen</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Sluizen</t>
+          <t>Ketsingen</t>
         </is>
       </c>
     </row>
@@ -5576,17 +5576,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>73083_13</t>
+          <t>73083_3</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Tongeren</t>
+          <t>Koninksem</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Tongeren</t>
+          <t>Koninksem</t>
         </is>
       </c>
     </row>
@@ -5596,17 +5596,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>73083_14</t>
+          <t>73083_4</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Vreren</t>
+          <t>Lauw</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Vreren</t>
+          <t>Lauw</t>
         </is>
       </c>
     </row>
@@ -5616,17 +5616,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>73083_15</t>
+          <t>73083_5</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Widooie</t>
+          <t>Mal</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Widooie</t>
+          <t>Mal</t>
         </is>
       </c>
     </row>
@@ -5636,17 +5636,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>73083_2</t>
+          <t>73083_6</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Ketsingen</t>
+          <t>Nerem</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Ketsingen</t>
+          <t>Nerem</t>
         </is>
       </c>
     </row>
@@ -5656,17 +5656,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>73083_3</t>
+          <t>73083_7</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Koninksem</t>
+          <t>Overrepen</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Koninksem</t>
+          <t>Overrepen</t>
         </is>
       </c>
     </row>
@@ -5676,17 +5676,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>73083_4</t>
+          <t>73083_8</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Lauw</t>
+          <t>Piringen</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Lauw</t>
+          <t>Piringen</t>
         </is>
       </c>
     </row>
@@ -5696,17 +5696,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>73083_5</t>
+          <t>73083_9</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Mal</t>
+          <t>Riksingen</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Mal</t>
+          <t>Riksingen</t>
         </is>
       </c>
     </row>
@@ -5716,17 +5716,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>73083_6</t>
+          <t>73098_1</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Nerem</t>
+          <t>Ulbeek</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Nerem</t>
+          <t>Ulbeek</t>
         </is>
       </c>
     </row>
@@ -5736,17 +5736,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>73083_7</t>
+          <t>73098_2</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Overrepen</t>
+          <t>Vrolingen</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Overrepen</t>
+          <t>Vrolingen</t>
         </is>
       </c>
     </row>
@@ -5756,17 +5756,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>73083_8</t>
+          <t>73098_3</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Piringen</t>
+          <t>Wellen</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Piringen</t>
+          <t>Wellen</t>
         </is>
       </c>
     </row>
@@ -5776,17 +5776,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>73083_9</t>
+          <t>73107_1</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Riksingen</t>
+          <t>Boorsem</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Riksingen</t>
+          <t>Boorsem</t>
         </is>
       </c>
     </row>
@@ -5796,17 +5796,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>73098_1</t>
+          <t>73107_10</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Ulbeek</t>
+          <t>Vucht</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Ulbeek</t>
+          <t>Vucht</t>
         </is>
       </c>
     </row>
@@ -5816,17 +5816,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>73098_2</t>
+          <t>73107_2</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Vrolingen</t>
+          <t>Eisden</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Vrolingen</t>
+          <t>Eisden</t>
         </is>
       </c>
     </row>
@@ -5836,17 +5836,17 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>73098_3</t>
+          <t>73107_4</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Wellen</t>
+          <t>Kotem</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Wellen</t>
+          <t>Kotem</t>
         </is>
       </c>
     </row>
@@ -5856,17 +5856,17 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>73107_1</t>
+          <t>73107_5</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Boorsem</t>
+          <t>Leut</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Boorsem</t>
+          <t>Leut</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>73107_10</t>
+          <t>73107_6</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Vucht</t>
+          <t>Mechelen-aan-de-Maas</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Vucht</t>
+          <t>Mechelen-aan-de-Maas</t>
         </is>
       </c>
     </row>
@@ -5896,17 +5896,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>73107_2</t>
+          <t>73107_7</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Eisden</t>
+          <t>Meeswijk</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Eisden</t>
+          <t>Meeswijk</t>
         </is>
       </c>
     </row>
@@ -5916,17 +5916,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>73107_3</t>
+          <t>73107_8</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Eisden-Tuinwijk</t>
+          <t>Opgrimbie</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Eisden-Tuinwijk</t>
+          <t>Opgrimbie</t>
         </is>
       </c>
     </row>
@@ -5936,17 +5936,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>73107_4</t>
+          <t>73107_9</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Kotem</t>
+          <t>Uikhoven</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Kotem</t>
+          <t>Uikhoven</t>
         </is>
       </c>
     </row>
@@ -5956,17 +5956,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>73107_5</t>
+          <t>73109_1</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Leut</t>
+          <t>Moelingen</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Leut</t>
+          <t>Moelingen</t>
         </is>
       </c>
     </row>
@@ -5976,17 +5976,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>73107_6</t>
+          <t>73109_2</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Maasmechelen-aan-de-Maas</t>
+          <t>'s Gravenvoeren</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Maasmechelen-aan-de-Maas</t>
+          <t>'s Gravenvoeren</t>
         </is>
       </c>
     </row>
@@ -5996,17 +5996,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>73107_7</t>
+          <t>73109_3</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Meeswijk</t>
+          <t>Sint-Martens-Voeren</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Meeswijk</t>
+          <t>Sint-Martens-Voeren</t>
         </is>
       </c>
     </row>
@@ -6016,17 +6016,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>73107_8</t>
+          <t>73109_4</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Opgrimbie</t>
+          <t>Teuven</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Opgrimbie</t>
+          <t>Teuven</t>
         </is>
       </c>
     </row>
@@ -6036,17 +6036,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>73107_9</t>
+          <t>RWM_MLO_BG</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Uikhoven</t>
+          <t>Buiten de kernen (Midden-Limburg Oost)</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Uikhoven</t>
+          <t>Buiten de kernen (Midden-Limburg Oost)</t>
         </is>
       </c>
     </row>
@@ -6056,17 +6056,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>73109_1</t>
+          <t>RWM_MLW_BG</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Moelingen</t>
+          <t>Buiten de kernen (Midden-Limburg West)</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Moelingen</t>
+          <t>Buiten de kernen (Midden-Limburg West)</t>
         </is>
       </c>
     </row>
@@ -6076,17 +6076,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>73109_2</t>
+          <t>RWM_NL_BG</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>'s Gravenvoeren</t>
+          <t>Buiten de kernen (Noord-Limburg)</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>'s Gravenvoeren</t>
+          <t>Buiten de kernen (Noord-Limburg)</t>
         </is>
       </c>
     </row>
@@ -6096,17 +6096,17 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>73109_3</t>
+          <t>RWM_NL_RE</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Sint-Martens-Voeren</t>
+          <t>Reppel-Kern</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Sint-Martens-Voeren</t>
+          <t>Reppel-Kern</t>
         </is>
       </c>
     </row>
@@ -6116,17 +6116,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>73109_4</t>
+          <t>RWM_NOL_BG</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Teuven</t>
+          <t>Buiten de kernen (Noordoost-Limburg)</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Teuven</t>
+          <t>Buiten de kernen (Noordoost-Limburg)</t>
         </is>
       </c>
     </row>
@@ -6136,17 +6136,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>RWM_MLO_BG</t>
+          <t>RWM_NWL_BG</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Buiten de kernen (Midden-Limburg Oost)</t>
+          <t>Buiten de kernen (Noordwest-Limburg)</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Buiten de kernen (Midden-Limburg Oost)</t>
+          <t>Buiten de kernen (Noordwest-Limburg)</t>
         </is>
       </c>
     </row>
@@ -6156,17 +6156,17 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>RWM_MLW_BG</t>
+          <t>RWM_OL_BG</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Buiten de kernen (Midden-Limburg West)</t>
+          <t>Buiten de kernen (Oost-Limburg)</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Buiten de kernen (Midden-Limburg West)</t>
+          <t>Buiten de kernen (Oost-Limburg)</t>
         </is>
       </c>
     </row>
@@ -6176,17 +6176,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>RWM_NL_BG</t>
+          <t>RWM_V_BG</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Buiten de kernen (Noord-Limburg)</t>
+          <t>Buiten de kernen (Voeren)</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Buiten de kernen (Noord-Limburg)</t>
+          <t>Buiten de kernen (Voeren)</t>
         </is>
       </c>
     </row>
@@ -6196,17 +6196,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>RWM_NL_RE</t>
+          <t>RWM_WL_BG</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Reppel</t>
+          <t>Buiten de kernen (West-Limburg)</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Reppel</t>
+          <t>Buiten de kernen (West-Limburg)</t>
         </is>
       </c>
     </row>
@@ -6216,17 +6216,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>RWM_NOL_BG</t>
+          <t>RWM_ZOL_BG</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Buiten de kernen (Noordoost-Limburg)</t>
+          <t>Buiten de kernen (Zuidoost-Limburg)</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Buiten de kernen (Noordoost-Limburg)</t>
+          <t>Buiten de kernen (Zuidoost-Limburg)</t>
         </is>
       </c>
     </row>
@@ -6236,115 +6236,15 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>RWM_NWL_BG</t>
+          <t>RWM_ZWL_BG</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Buiten de kernen (Noordwest-Limburg)</t>
+          <t>Buiten de kernen (Zuidwest-Limburg)</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
-        <is>
-          <t>Buiten de kernen (Noordwest-Limburg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>291</v>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>RWM_OL_BG</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Buiten de kernen (Oost-Limburg)</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>Buiten de kernen (Oost-Limburg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>292</v>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>RWM_V_BG</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Buiten de kernen (Voeren)</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>Buiten de kernen (Voeren)</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>293</v>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>RWM_WL_BG</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Buiten de kernen (West-Limburg)</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>Buiten de kernen (West-Limburg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>294</v>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>RWM_ZOL_BG</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Buiten de kernen (Zuidoost-Limburg)</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>Buiten de kernen (Zuidoost-Limburg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>295</v>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>RWM_ZWL_BG</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Buiten de kernen (Zuidwest-Limburg)</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
         <is>
           <t>Buiten de kernen (Zuidwest-Limburg)</t>
         </is>
